--- a/sampleprojects/TaxReturn/excel/states/GA.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/GA.xlsx
@@ -83,7 +83,7 @@
     <t>MFJ/QSS: $24,000 std ded, 5.39%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 24000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0539</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 24000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0539</t>
   </si>
   <si>
     <t>X</t>
@@ -92,13 +92,13 @@
     <t>HOH: $18,000 std ded, 5.39%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 18000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0539</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 18000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0539</t>
   </si>
   <si>
     <t>Default (Single/MFS): $12,000 std ded, 5.39%</t>
   </si>
   <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.agi - 12000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0539</t>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 12000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0539</t>
   </si>
   <si>
     <t>Policy:</t>

--- a/sampleprojects/TaxReturn/excel/states/GA.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/GA.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="GA Tax" sheetId="2" r:id="rId4"/>
-    <sheet name="EDD" sheetId="3" r:id="rId6"/>
+    <sheet name="GA Retirement Income Exclusion" sheetId="3" r:id="rId6"/>
+    <sheet name="EDD" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
   <si>
     <t>DT: GA Tax</t>
   </si>
@@ -44,7 +45,7 @@
     <t/>
   </si>
   <si>
-    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  Georgia Tax Calculation (top marginal 5.39%)" to job.audit_trail</t>
+    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  Georgia Tax Calculation (flat 5.19%, 2025)" to job.audit_trail; set result.ga_military_retirement_exemption = 0.0; perform GA_Retirement_Income_Exclusion; add "  GA Schedule 1 line 7 retirement/military exclusion: $" + result.ga_military_retirement_exemption to job.audit_trail</t>
   </si>
   <si>
     <t>CONDITIONS: COMMENTS</t>
@@ -80,25 +81,25 @@
     <t>DSL: ACTIONS</t>
   </si>
   <si>
-    <t>MFJ/QSS: $24,000 std ded, 5.39%</t>
-  </si>
-  <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 24000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0539</t>
+    <t>MFJ/QSS: $24,000 std ded, 5.19% (2025, HB 111)</t>
+  </si>
+  <si>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.ga_military_retirement_exemption - 24000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * ga_tax_rate</t>
   </si>
   <si>
     <t>X</t>
   </si>
   <si>
-    <t>HOH: $18,000 std ded, 5.39%</t>
-  </si>
-  <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 18000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0539</t>
-  </si>
-  <si>
-    <t>Default (Single/MFS): $12,000 std ded, 5.39%</t>
-  </si>
-  <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 12000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0539</t>
+    <t>HOH: $18,000 std ded, 5.19% (2025, HB 111)</t>
+  </si>
+  <si>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.ga_military_retirement_exemption - 18000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * ga_tax_rate</t>
+  </si>
+  <si>
+    <t>Default (Single/MFS): $12,000 std ded, 5.19% (2025, HB 111)</t>
+  </si>
+  <si>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.ga_military_retirement_exemption - 12000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * ga_tax_rate</t>
   </si>
   <si>
     <t>Policy:</t>
@@ -107,13 +108,88 @@
     <t>Policy Statements</t>
   </si>
   <si>
-    <t>GA MFJ: 5.39% x max(AGI - $24,000, 0) per OCGA § 48-7-20</t>
-  </si>
-  <si>
-    <t>GA HOH: 5.39% x max(AGI - $18,000, 0) per OCGA § 48-7-20</t>
-  </si>
-  <si>
-    <t>GA Single/MFS: 5.39% x max(AGI - $12,000, 0) per OCGA § 48-7-20</t>
+    <t>GA MFJ: 5.19% x max(AGI - $24,000, 0) per OCGA § 48-7-20 Georgia AGI is federal AGI less the Schedule 1 line 7 exclusion of military retired pay (GA_Retirement_Income_Exclusion).</t>
+  </si>
+  <si>
+    <t>GA HOH: 5.19% x max(AGI - $18,000, 0) per OCGA § 48-7-20 Georgia AGI is federal AGI less the Schedule 1 line 7 exclusion of military retired pay (GA_Retirement_Income_Exclusion).</t>
+  </si>
+  <si>
+    <t>GA Single/MFS: 5.19% x max(AGI - $12,000, 0) per OCGA § 48-7-20 Georgia AGI is federal AGI less the Schedule 1 line 7 exclusion of military retired pay (GA_Retirement_Income_Exclusion).</t>
+  </si>
+  <si>
+    <t>DT: GA Retirement Income Exclusion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMMENTS: </t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 51201</t>
+  </si>
+  <si>
+    <t>for all taxpayers</t>
+  </si>
+  <si>
+    <t>The taxpayer has military retired pay (a taxable pension on Schedule 1 worksheet line 12)</t>
+  </si>
+  <si>
+    <t>taxpayer.military_retirement_pay &gt; 0</t>
+  </si>
+  <si>
+    <t>Under 62 at year end: the military retirement income exclusion, Schedule 1 line 7b</t>
+  </si>
+  <si>
+    <t>job.tax_year - (get yearof taxpayer.date_of_birth) &lt; 62</t>
+  </si>
+  <si>
+    <t>More than $17,500 of Georgia earned income: an additional $17,500</t>
+  </si>
+  <si>
+    <t>taxpayer.w2_wages &gt; ga_military_exemption_under_62_earned_threshold</t>
+  </si>
+  <si>
+    <t>65 or older: $65,000 retirement income exclusion</t>
+  </si>
+  <si>
+    <t>job.tax_year - (get yearof taxpayer.date_of_birth) &gt;= 65</t>
+  </si>
+  <si>
+    <t>Schedule 1 line 7b: $17,500 plus an additional $17,500 when earned income exceeds $17,500 (O.C.G.A. 48-7-27(a)(5.1))</t>
+  </si>
+  <si>
+    <t>add the minimum of taxpayer.military_retirement_pay and (ga_military_exemption_under_62_base * 2.0) to result.ga_military_retirement_exemption</t>
+  </si>
+  <si>
+    <t>Schedule 1 line 7b: up to $17,500 of military retirement income</t>
+  </si>
+  <si>
+    <t>add the minimum of taxpayer.military_retirement_pay and ga_military_exemption_under_62_base to result.ga_military_retirement_exemption</t>
+  </si>
+  <si>
+    <t>Schedule 1 line 7a worksheet: earned income up to $5,000 (lines 3-5) plus taxable pensions (line 12), capped at $65,000 (line 16)</t>
+  </si>
+  <si>
+    <t>add the minimum of ((the minimum of taxpayer.w2_wages and ga_retirement_exclusion_earned_income_cap) + taxpayer.military_retirement_pay) and ga_military_exemption_65_plus to result.ga_military_retirement_exemption</t>
+  </si>
+  <si>
+    <t>Schedule 1 line 7a worksheet: earned income up to $5,000 plus taxable pensions, capped at $35,000 at age 62-64</t>
+  </si>
+  <si>
+    <t>add the minimum of ((the minimum of taxpayer.w2_wages and ga_retirement_exclusion_earned_income_cap) + taxpayer.military_retirement_pay) and ga_military_exemption_62_to_64 to result.ga_military_retirement_exemption</t>
+  </si>
+  <si>
+    <t>Under 62 with Georgia earned income over $17,500: military retirement income exclusion of up to $35,000 (Form 500 Schedule 1 line 7b; O.C.G.A. 48-7-27(a)(5.1); 2025 IT-511 p. 20-21).</t>
+  </si>
+  <si>
+    <t>Under 62: military retirement income exclusion of up to $17,500 (Schedule 1 line 7b).</t>
+  </si>
+  <si>
+    <t>65 or older: the retirement income exclusion (Schedule 1 line 7a; O.C.G.A. 48-7-27(a)(5)), up to $65,000 of the military pension plus up to $5,000 of earned income. Other unearned income that also counts (interest, dividends, other pensions) is not modelled.</t>
+  </si>
+  <si>
+    <t>62 to 64: the retirement income exclusion, up to $35,000 of the military pension plus up to $5,000 of earned income (Schedule 1 line 7a). Line 7b is for taxpayers under 62 only.</t>
+  </si>
+  <si>
+    <t>No military retired pay for this taxpayer; the retirement income exclusion for other income is not modelled (#1200).</t>
   </si>
   <si>
     <t>EDD: EDD</t>
@@ -161,7 +237,7 @@
     <t>result</t>
   </si>
   <si>
-    <t>(6 attributes)</t>
+    <t>(8 attributes)</t>
   </si>
   <si>
     <t>ga_military_exemption_62_to_64</t>
@@ -176,7 +252,7 @@
     <t>r</t>
   </si>
   <si>
-    <t>GA military retirement exemption age 62-64 (2025). Source: MOAA</t>
+    <t>Georgia retirement income exclusion cap at age 62-64 (or under 62 and permanently disabled): $35,000, covering taxable pensions including military retired pay plus up to $5,000 of earned income. Form 500 Schedule 1 line 7a; O.C.G.A. 48-7-27(a)(5); 2025 IT-511 p. 20-21. The military exclusion on line 7b is for taxpayers under 62 only.</t>
   </si>
   <si>
     <t>ga_military_exemption_65_plus</t>
@@ -185,7 +261,7 @@
     <t>65000.0</t>
   </si>
   <si>
-    <t>GA military retirement exemption age 65+ (2025). Source: MOAA</t>
+    <t>Georgia retirement income exclusion cap at age 65 or older: $65,000 per taxpayer, covering taxable pensions including military retired pay plus up to $5,000 of earned income. Form 500 Schedule 1 line 7a; O.C.G.A. 48-7-27(a)(5); 2025 IT-511 p. 20-21.</t>
   </si>
   <si>
     <t>ga_military_exemption_under_62_base</t>
@@ -194,7 +270,7 @@
     <t>17500.0</t>
   </si>
   <si>
-    <t>GA military retirement base exemption under age 62 (2025). Source: MOAA</t>
+    <t>Georgia military retirement income exclusion for a taxpayer under 62: up to $17,500, plus an additional $17,500 when Georgia earned income exceeds $17,500. Form 500 Schedule 1 line 7b; O.C.G.A. 48-7-27(a)(5.1); 2025 IT-511 p. 20-21.</t>
   </si>
   <si>
     <t>ga_military_exemption_under_62_earned_threshold</t>
@@ -209,13 +285,31 @@
     <t>0.0</t>
   </si>
   <si>
-    <t>GA military retirement exemption (computed based on age and earned income)</t>
+    <t>Georgia exclusion of military retired pay, computed per taxpayer by GA_Retirement_Income_Exclusion: under 62, the military retirement exclusion (Schedule 1 line 7b); 62 and over, the retirement income exclusion (line 7a) counting the pay as a taxable pension and up to $5,000 of wages as earned income (#1330).</t>
   </si>
   <si>
     <t>ga_military_retirement_taxable</t>
   </si>
   <si>
     <t>GA taxable military retirement after exemption (computed)</t>
+  </si>
+  <si>
+    <t>ga_retirement_exclusion_earned_income_cap</t>
+  </si>
+  <si>
+    <t>5000.0</t>
+  </si>
+  <si>
+    <t>Georgia retirement income exclusion (Form 500 Schedule 1 line 7a): up to $5,000 of the maximum exclusion may be earned income (2025 IT-511 Schedule 1 worksheet lines 4-5).</t>
+  </si>
+  <si>
+    <t>ga_tax_rate</t>
+  </si>
+  <si>
+    <t>0.0519</t>
+  </si>
+  <si>
+    <t>Georgia flat income tax rate 5.19% effective January 1, 2025 (HB 111; 2025 IT-511 What is New; Form 500 line 16). Was 5.39% for 2024.</t>
   </si>
 </sst>
 </file>
@@ -1503,6 +1597,1140 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
+    <col customWidth="true" max="1" min="1" width="20"/>
+    <col customWidth="true" max="3" min="2" width="40"/>
+    <col customWidth="true" max="19" min="4" width="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1">
+        <v>3</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4</v>
+      </c>
+      <c r="H11" s="1">
+        <v>5</v>
+      </c>
+      <c r="I11" s="1">
+        <v>6</v>
+      </c>
+      <c r="J11" s="1">
+        <v>7</v>
+      </c>
+      <c r="K11" s="1">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1">
+        <v>9</v>
+      </c>
+      <c r="M11" s="1">
+        <v>10</v>
+      </c>
+      <c r="N11" s="1">
+        <v>11</v>
+      </c>
+      <c r="O11" s="1">
+        <v>12</v>
+      </c>
+      <c r="P11" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>14</v>
+      </c>
+      <c r="R11" s="1">
+        <v>15</v>
+      </c>
+      <c r="S11" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4">
+        <v>2</v>
+      </c>
+      <c r="F17" s="4">
+        <v>3</v>
+      </c>
+      <c r="G17" s="4">
+        <v>4</v>
+      </c>
+      <c r="H17" s="4">
+        <v>5</v>
+      </c>
+      <c r="I17" s="4">
+        <v>6</v>
+      </c>
+      <c r="J17" s="4">
+        <v>7</v>
+      </c>
+      <c r="K17" s="4">
+        <v>8</v>
+      </c>
+      <c r="L17" s="4">
+        <v>9</v>
+      </c>
+      <c r="M17" s="4">
+        <v>10</v>
+      </c>
+      <c r="N17" s="4">
+        <v>11</v>
+      </c>
+      <c r="O17" s="4">
+        <v>12</v>
+      </c>
+      <c r="P17" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>14</v>
+      </c>
+      <c r="R17" s="4">
+        <v>15</v>
+      </c>
+      <c r="S17" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5">
+        <v>1</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5">
+        <v>2</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5">
+        <v>3</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5">
+        <v>4</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1">
+        <v>2</v>
+      </c>
+      <c r="F23" s="1">
+        <v>3</v>
+      </c>
+      <c r="G23" s="1">
+        <v>4</v>
+      </c>
+      <c r="H23" s="1">
+        <v>5</v>
+      </c>
+      <c r="I23" s="1">
+        <v>6</v>
+      </c>
+      <c r="J23" s="1">
+        <v>7</v>
+      </c>
+      <c r="K23" s="1">
+        <v>8</v>
+      </c>
+      <c r="L23" s="1">
+        <v>9</v>
+      </c>
+      <c r="M23" s="1">
+        <v>10</v>
+      </c>
+      <c r="N23" s="1">
+        <v>11</v>
+      </c>
+      <c r="O23" s="1">
+        <v>12</v>
+      </c>
+      <c r="P23" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>14</v>
+      </c>
+      <c r="R23" s="1">
+        <v>15</v>
+      </c>
+      <c r="S23" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5">
+        <v>1</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5">
+        <v>2</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5">
+        <v>3</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5">
+        <v>4</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5">
+        <v>5</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:S6"/>
+    <mergeCell ref="C7:S7"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A23:B23"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
     <col customWidth="true" max="1" min="1" width="18"/>
     <col customWidth="true" max="2" min="2" width="25"/>
     <col customWidth="true" max="3" min="3" width="10"/>
@@ -1519,56 +2747,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>39</v>
+        <v>64</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -1587,25 +2815,25 @@
         <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>53</v>
+        <v>78</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>8</v>
@@ -1628,25 +2856,25 @@
         <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>8</v>
@@ -1669,25 +2897,25 @@
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>8</v>
@@ -1710,25 +2938,25 @@
         <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>8</v>
@@ -1751,25 +2979,25 @@
         <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>8</v>
@@ -1792,25 +3020,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>8</v>
@@ -1825,6 +3053,88 @@
         <v>8</v>
       </c>
       <c r="M9" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M11" s="8" t="s">
         <v>8</v>
       </c>
     </row>

--- a/sampleprojects/TaxReturn/excel/states/GA.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/GA.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
   <si>
     <t>DT: GA Tax</t>
   </si>
@@ -153,6 +153,12 @@
     <t>job.tax_year - (get yearof taxpayer.date_of_birth) &gt;= 65</t>
   </si>
   <si>
+    <t>Full-year resident entry only. A part-year or nonresident entry's income is built from the income entities, so the pension is not in it, and 4 U.S.C. 114 bars a state from taxing a nonresident's retirement income (#1330 review).</t>
+  </si>
+  <si>
+    <t>result.state_calc_resident_status is equal to "full_year"</t>
+  </si>
+  <si>
     <t>Schedule 1 line 7b: $17,500 plus an additional $17,500 when earned income exceeds $17,500 (O.C.G.A. 48-7-27(a)(5.1))</t>
   </si>
   <si>
@@ -190,6 +196,9 @@
   </si>
   <si>
     <t>No military retired pay for this taxpayer; the retirement income exclusion for other income is not modelled (#1200).</t>
+  </si>
+  <si>
+    <t>Not a full-year resident entry: the pension is not in this entry's sourced income (the roster builds it from the income entities) and 4 U.S.C. 114 bars taxing a nonresident's retirement income, so nothing is subtracted.</t>
   </si>
   <si>
     <t>EDD: EDD</t>
@@ -1854,7 +1863,7 @@
         <v>15</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>8</v>
@@ -1913,7 +1922,7 @@
         <v>18</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>8</v>
@@ -1972,7 +1981,7 @@
         <v>18</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>8</v>
@@ -2031,7 +2040,7 @@
         <v>18</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>8</v>
@@ -2064,125 +2073,125 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="s">
+    <row r="16">
+      <c r="A16" s="5">
+        <v>5</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1" t="s">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D18" s="4">
         <v>1</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E18" s="4">
         <v>2</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F18" s="4">
         <v>3</v>
       </c>
-      <c r="G17" s="4">
+      <c r="G18" s="4">
         <v>4</v>
       </c>
-      <c r="H17" s="4">
+      <c r="H18" s="4">
         <v>5</v>
       </c>
-      <c r="I17" s="4">
+      <c r="I18" s="4">
         <v>6</v>
       </c>
-      <c r="J17" s="4">
+      <c r="J18" s="4">
         <v>7</v>
       </c>
-      <c r="K17" s="4">
-        <v>8</v>
-      </c>
-      <c r="L17" s="4">
+      <c r="K18" s="4">
+        <v>8</v>
+      </c>
+      <c r="L18" s="4">
         <v>9</v>
       </c>
-      <c r="M17" s="4">
+      <c r="M18" s="4">
         <v>10</v>
       </c>
-      <c r="N17" s="4">
+      <c r="N18" s="4">
         <v>11</v>
       </c>
-      <c r="O17" s="4">
+      <c r="O18" s="4">
         <v>12</v>
       </c>
-      <c r="P17" s="4">
+      <c r="P18" s="4">
         <v>13</v>
       </c>
-      <c r="Q17" s="4">
+      <c r="Q18" s="4">
         <v>14</v>
       </c>
-      <c r="R17" s="4">
+      <c r="R18" s="4">
         <v>15</v>
       </c>
-      <c r="S17" s="4">
+      <c r="S18" s="4">
         <v>16</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5">
-        <v>1</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>47</v>
@@ -2191,10 +2200,10 @@
         <v>48</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>8</v>
@@ -2241,7 +2250,7 @@
     </row>
     <row r="20">
       <c r="A20" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>49</v>
@@ -2253,10 +2262,10 @@
         <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>8</v>
@@ -2300,7 +2309,7 @@
     </row>
     <row r="21">
       <c r="A21" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>51</v>
@@ -2315,170 +2324,170 @@
         <v>8</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="G21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5">
+        <v>4</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="H21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S21" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="s">
+      <c r="H22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1" t="s">
+      <c r="B24" s="1"/>
+      <c r="C24" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D24" s="1">
         <v>1</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E24" s="1">
         <v>2</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F24" s="1">
         <v>3</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G24" s="1">
         <v>4</v>
       </c>
-      <c r="H23" s="1">
+      <c r="H24" s="1">
         <v>5</v>
       </c>
-      <c r="I23" s="1">
+      <c r="I24" s="1">
         <v>6</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J24" s="1">
         <v>7</v>
       </c>
-      <c r="K23" s="1">
-        <v>8</v>
-      </c>
-      <c r="L23" s="1">
+      <c r="K24" s="1">
+        <v>8</v>
+      </c>
+      <c r="L24" s="1">
         <v>9</v>
       </c>
-      <c r="M23" s="1">
+      <c r="M24" s="1">
         <v>10</v>
       </c>
-      <c r="N23" s="1">
+      <c r="N24" s="1">
         <v>11</v>
       </c>
-      <c r="O23" s="1">
+      <c r="O24" s="1">
         <v>12</v>
       </c>
-      <c r="P23" s="1">
+      <c r="P24" s="1">
         <v>13</v>
       </c>
-      <c r="Q23" s="1">
+      <c r="Q24" s="1">
         <v>14</v>
       </c>
-      <c r="R23" s="1">
+      <c r="R24" s="1">
         <v>15</v>
       </c>
-      <c r="S23" s="1">
+      <c r="S24" s="1">
         <v>16</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5">
-        <v>1</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S24" s="2" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>8</v>
@@ -2534,10 +2543,10 @@
     </row>
     <row r="26">
       <c r="A26" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>8</v>
@@ -2593,10 +2602,10 @@
     </row>
     <row r="27">
       <c r="A27" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>8</v>
@@ -2652,60 +2661,178 @@
     </row>
     <row r="28">
       <c r="A28" s="5">
+        <v>4</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5">
         <v>5</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="S28" s="2" t="s">
+      <c r="B29" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5">
+        <v>6</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S30" s="2" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2721,8 +2848,8 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="C9:S9"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A24:B24"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -2747,56 +2874,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -2815,25 +2942,25 @@
         <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>8</v>
@@ -2856,25 +2983,25 @@
         <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>77</v>
-      </c>
       <c r="H5" s="16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>8</v>
@@ -2897,25 +3024,25 @@
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>8</v>
@@ -2938,25 +3065,25 @@
         <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>8</v>
@@ -2979,25 +3106,25 @@
         <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>8</v>
@@ -3020,25 +3147,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>8</v>
@@ -3061,25 +3188,25 @@
         <v>8</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>8</v>
@@ -3102,25 +3229,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>8</v>

--- a/sampleprojects/TaxReturn/excel/states/GA.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/GA.xlsx
@@ -8,14 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="GA Tax" sheetId="2" r:id="rId4"/>
-    <sheet name="EDD" sheetId="3" r:id="rId6"/>
+    <sheet name="GA Retirement Income Exclusion" sheetId="3" r:id="rId6"/>
+    <sheet name="EDD" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
   <si>
     <t>DT: GA Tax</t>
   </si>
@@ -44,7 +45,7 @@
     <t/>
   </si>
   <si>
-    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  Georgia Tax Calculation (top marginal 5.39%)" to job.audit_trail</t>
+    <t>set result.computed_state_tax = 0; set result.computed_state_taxable_income = 0; add "  Georgia Tax Calculation (flat 5.19%, 2025)" to job.audit_trail; set result.ga_military_retirement_exemption = 0.0; perform GA_Retirement_Income_Exclusion; add "  GA Schedule 1 line 7 retirement/military exclusion: $" + result.ga_military_retirement_exemption to job.audit_trail</t>
   </si>
   <si>
     <t>CONDITIONS: COMMENTS</t>
@@ -80,25 +81,25 @@
     <t>DSL: ACTIONS</t>
   </si>
   <si>
-    <t>MFJ/QSS: $24,000 std ded, 5.39%</t>
-  </si>
-  <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 24000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0539</t>
+    <t>MFJ/QSS: $24,000 std ded, 5.19% (2025, HB 111)</t>
+  </si>
+  <si>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.ga_military_retirement_exemption - 24000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * ga_tax_rate</t>
   </si>
   <si>
     <t>X</t>
   </si>
   <si>
-    <t>HOH: $18,000 std ded, 5.39%</t>
-  </si>
-  <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 18000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0539</t>
-  </si>
-  <si>
-    <t>Default (Single/MFS): $12,000 std ded, 5.39%</t>
-  </si>
-  <si>
-    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - 12000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * 0.0539</t>
+    <t>HOH: $18,000 std ded, 5.19% (2025, HB 111)</t>
+  </si>
+  <si>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.ga_military_retirement_exemption - 18000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * ga_tax_rate</t>
+  </si>
+  <si>
+    <t>Default (Single/MFS): $12,000 std ded, 5.19% (2025, HB 111)</t>
+  </si>
+  <si>
+    <t>set result.computed_state_taxable_income = the maximum of (result.state_calc_agi - result.ga_military_retirement_exemption - 12000.0) and 0.0; set result.computed_state_tax = result.computed_state_taxable_income * ga_tax_rate</t>
   </si>
   <si>
     <t>Policy:</t>
@@ -107,13 +108,97 @@
     <t>Policy Statements</t>
   </si>
   <si>
-    <t>GA MFJ: 5.39% x max(AGI - $24,000, 0) per OCGA § 48-7-20</t>
-  </si>
-  <si>
-    <t>GA HOH: 5.39% x max(AGI - $18,000, 0) per OCGA § 48-7-20</t>
-  </si>
-  <si>
-    <t>GA Single/MFS: 5.39% x max(AGI - $12,000, 0) per OCGA § 48-7-20</t>
+    <t>GA MFJ: 5.19% x max(AGI - $24,000, 0) per OCGA § 48-7-20 Georgia AGI is federal AGI less the Schedule 1 line 7 exclusion of military retired pay (GA_Retirement_Income_Exclusion).</t>
+  </si>
+  <si>
+    <t>GA HOH: 5.19% x max(AGI - $18,000, 0) per OCGA § 48-7-20 Georgia AGI is federal AGI less the Schedule 1 line 7 exclusion of military retired pay (GA_Retirement_Income_Exclusion).</t>
+  </si>
+  <si>
+    <t>GA Single/MFS: 5.19% x max(AGI - $12,000, 0) per OCGA § 48-7-20 Georgia AGI is federal AGI less the Schedule 1 line 7 exclusion of military retired pay (GA_Retirement_Income_Exclusion).</t>
+  </si>
+  <si>
+    <t>DT: GA Retirement Income Exclusion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMMENTS: </t>
+  </si>
+  <si>
+    <t>TABLE_NUMBER: 51201</t>
+  </si>
+  <si>
+    <t>for all taxpayers</t>
+  </si>
+  <si>
+    <t>The taxpayer has military retired pay (a taxable pension on Schedule 1 worksheet line 12)</t>
+  </si>
+  <si>
+    <t>taxpayer.military_retirement_pay &gt; 0</t>
+  </si>
+  <si>
+    <t>Under 62 at year end: the military retirement income exclusion, Schedule 1 line 7b</t>
+  </si>
+  <si>
+    <t>job.tax_year - (get yearof taxpayer.date_of_birth) &lt; 62</t>
+  </si>
+  <si>
+    <t>More than $17,500 of Georgia earned income: an additional $17,500</t>
+  </si>
+  <si>
+    <t>taxpayer.w2_wages &gt; ga_military_exemption_under_62_earned_threshold</t>
+  </si>
+  <si>
+    <t>65 or older: $65,000 retirement income exclusion</t>
+  </si>
+  <si>
+    <t>job.tax_year - (get yearof taxpayer.date_of_birth) &gt;= 65</t>
+  </si>
+  <si>
+    <t>Full-year resident entry only. A part-year or nonresident entry's income is built from the income entities, so the pension is not in it, and 4 U.S.C. 114 bars a state from taxing a nonresident's retirement income (#1330 review).</t>
+  </si>
+  <si>
+    <t>result.state_calc_resident_status is equal to "full_year"</t>
+  </si>
+  <si>
+    <t>Schedule 1 line 7b: $17,500 plus an additional $17,500 when earned income exceeds $17,500 (O.C.G.A. 48-7-27(a)(5.1))</t>
+  </si>
+  <si>
+    <t>add the minimum of taxpayer.military_retirement_pay and (ga_military_exemption_under_62_base * 2.0) to result.ga_military_retirement_exemption</t>
+  </si>
+  <si>
+    <t>Schedule 1 line 7b: up to $17,500 of military retirement income</t>
+  </si>
+  <si>
+    <t>add the minimum of taxpayer.military_retirement_pay and ga_military_exemption_under_62_base to result.ga_military_retirement_exemption</t>
+  </si>
+  <si>
+    <t>Schedule 1 line 7a worksheet: earned income up to $5,000 (lines 3-5) plus taxable pensions (line 12), capped at $65,000 (line 16)</t>
+  </si>
+  <si>
+    <t>add the minimum of ((the minimum of taxpayer.w2_wages and ga_retirement_exclusion_earned_income_cap) + taxpayer.military_retirement_pay) and ga_military_exemption_65_plus to result.ga_military_retirement_exemption</t>
+  </si>
+  <si>
+    <t>Schedule 1 line 7a worksheet: earned income up to $5,000 plus taxable pensions, capped at $35,000 at age 62-64</t>
+  </si>
+  <si>
+    <t>add the minimum of ((the minimum of taxpayer.w2_wages and ga_retirement_exclusion_earned_income_cap) + taxpayer.military_retirement_pay) and ga_military_exemption_62_to_64 to result.ga_military_retirement_exemption</t>
+  </si>
+  <si>
+    <t>Under 62 with Georgia earned income over $17,500: military retirement income exclusion of up to $35,000 (Form 500 Schedule 1 line 7b; O.C.G.A. 48-7-27(a)(5.1); 2025 IT-511 p. 20-21).</t>
+  </si>
+  <si>
+    <t>Under 62: military retirement income exclusion of up to $17,500 (Schedule 1 line 7b).</t>
+  </si>
+  <si>
+    <t>65 or older: the retirement income exclusion (Schedule 1 line 7a; O.C.G.A. 48-7-27(a)(5)), up to $65,000 of the military pension plus up to $5,000 of earned income. Other unearned income that also counts (interest, dividends, other pensions) is not modelled.</t>
+  </si>
+  <si>
+    <t>62 to 64: the retirement income exclusion, up to $35,000 of the military pension plus up to $5,000 of earned income (Schedule 1 line 7a). Line 7b is for taxpayers under 62 only.</t>
+  </si>
+  <si>
+    <t>No military retired pay for this taxpayer; the retirement income exclusion for other income is not modelled (#1200).</t>
+  </si>
+  <si>
+    <t>Not a full-year resident entry: the pension is not in this entry's sourced income (the roster builds it from the income entities) and 4 U.S.C. 114 bars taxing a nonresident's retirement income, so nothing is subtracted.</t>
   </si>
   <si>
     <t>EDD: EDD</t>
@@ -161,7 +246,7 @@
     <t>result</t>
   </si>
   <si>
-    <t>(6 attributes)</t>
+    <t>(8 attributes)</t>
   </si>
   <si>
     <t>ga_military_exemption_62_to_64</t>
@@ -176,7 +261,7 @@
     <t>r</t>
   </si>
   <si>
-    <t>GA military retirement exemption age 62-64 (2025). Source: MOAA</t>
+    <t>Georgia retirement income exclusion cap at age 62-64 (or under 62 and permanently disabled): $35,000, covering taxable pensions including military retired pay plus up to $5,000 of earned income. Form 500 Schedule 1 line 7a; O.C.G.A. 48-7-27(a)(5); 2025 IT-511 p. 20-21. The military exclusion on line 7b is for taxpayers under 62 only.</t>
   </si>
   <si>
     <t>ga_military_exemption_65_plus</t>
@@ -185,7 +270,7 @@
     <t>65000.0</t>
   </si>
   <si>
-    <t>GA military retirement exemption age 65+ (2025). Source: MOAA</t>
+    <t>Georgia retirement income exclusion cap at age 65 or older: $65,000 per taxpayer, covering taxable pensions including military retired pay plus up to $5,000 of earned income. Form 500 Schedule 1 line 7a; O.C.G.A. 48-7-27(a)(5); 2025 IT-511 p. 20-21.</t>
   </si>
   <si>
     <t>ga_military_exemption_under_62_base</t>
@@ -194,7 +279,7 @@
     <t>17500.0</t>
   </si>
   <si>
-    <t>GA military retirement base exemption under age 62 (2025). Source: MOAA</t>
+    <t>Georgia military retirement income exclusion for a taxpayer under 62: up to $17,500, plus an additional $17,500 when Georgia earned income exceeds $17,500. Form 500 Schedule 1 line 7b; O.C.G.A. 48-7-27(a)(5.1); 2025 IT-511 p. 20-21.</t>
   </si>
   <si>
     <t>ga_military_exemption_under_62_earned_threshold</t>
@@ -209,13 +294,31 @@
     <t>0.0</t>
   </si>
   <si>
-    <t>GA military retirement exemption (computed based on age and earned income)</t>
+    <t>Georgia exclusion of military retired pay, computed per taxpayer by GA_Retirement_Income_Exclusion: under 62, the military retirement exclusion (Schedule 1 line 7b); 62 and over, the retirement income exclusion (line 7a) counting the pay as a taxable pension and up to $5,000 of wages as earned income (#1330).</t>
   </si>
   <si>
     <t>ga_military_retirement_taxable</t>
   </si>
   <si>
     <t>GA taxable military retirement after exemption (computed)</t>
+  </si>
+  <si>
+    <t>ga_retirement_exclusion_earned_income_cap</t>
+  </si>
+  <si>
+    <t>5000.0</t>
+  </si>
+  <si>
+    <t>Georgia retirement income exclusion (Form 500 Schedule 1 line 7a): up to $5,000 of the maximum exclusion may be earned income (2025 IT-511 Schedule 1 worksheet lines 4-5).</t>
+  </si>
+  <si>
+    <t>ga_tax_rate</t>
+  </si>
+  <si>
+    <t>0.0519</t>
+  </si>
+  <si>
+    <t>Georgia flat income tax rate 5.19% effective January 1, 2025 (HB 111; 2025 IT-511 What is New; Form 500 line 16). Was 5.39% for 2024.</t>
   </si>
 </sst>
 </file>
@@ -1503,6 +1606,1258 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
+    <col customWidth="true" max="1" min="1" width="20"/>
+    <col customWidth="true" max="3" min="2" width="40"/>
+    <col customWidth="true" max="19" min="4" width="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>2</v>
+      </c>
+      <c r="F11" s="1">
+        <v>3</v>
+      </c>
+      <c r="G11" s="1">
+        <v>4</v>
+      </c>
+      <c r="H11" s="1">
+        <v>5</v>
+      </c>
+      <c r="I11" s="1">
+        <v>6</v>
+      </c>
+      <c r="J11" s="1">
+        <v>7</v>
+      </c>
+      <c r="K11" s="1">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1">
+        <v>9</v>
+      </c>
+      <c r="M11" s="1">
+        <v>10</v>
+      </c>
+      <c r="N11" s="1">
+        <v>11</v>
+      </c>
+      <c r="O11" s="1">
+        <v>12</v>
+      </c>
+      <c r="P11" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>14</v>
+      </c>
+      <c r="R11" s="1">
+        <v>15</v>
+      </c>
+      <c r="S11" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5">
+        <v>1</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5">
+        <v>2</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5">
+        <v>3</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5">
+        <v>5</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4">
+        <v>2</v>
+      </c>
+      <c r="F18" s="4">
+        <v>3</v>
+      </c>
+      <c r="G18" s="4">
+        <v>4</v>
+      </c>
+      <c r="H18" s="4">
+        <v>5</v>
+      </c>
+      <c r="I18" s="4">
+        <v>6</v>
+      </c>
+      <c r="J18" s="4">
+        <v>7</v>
+      </c>
+      <c r="K18" s="4">
+        <v>8</v>
+      </c>
+      <c r="L18" s="4">
+        <v>9</v>
+      </c>
+      <c r="M18" s="4">
+        <v>10</v>
+      </c>
+      <c r="N18" s="4">
+        <v>11</v>
+      </c>
+      <c r="O18" s="4">
+        <v>12</v>
+      </c>
+      <c r="P18" s="4">
+        <v>13</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>14</v>
+      </c>
+      <c r="R18" s="4">
+        <v>15</v>
+      </c>
+      <c r="S18" s="4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5">
+        <v>1</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5">
+        <v>2</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5">
+        <v>3</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5">
+        <v>4</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1">
+        <v>2</v>
+      </c>
+      <c r="F24" s="1">
+        <v>3</v>
+      </c>
+      <c r="G24" s="1">
+        <v>4</v>
+      </c>
+      <c r="H24" s="1">
+        <v>5</v>
+      </c>
+      <c r="I24" s="1">
+        <v>6</v>
+      </c>
+      <c r="J24" s="1">
+        <v>7</v>
+      </c>
+      <c r="K24" s="1">
+        <v>8</v>
+      </c>
+      <c r="L24" s="1">
+        <v>9</v>
+      </c>
+      <c r="M24" s="1">
+        <v>10</v>
+      </c>
+      <c r="N24" s="1">
+        <v>11</v>
+      </c>
+      <c r="O24" s="1">
+        <v>12</v>
+      </c>
+      <c r="P24" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q24" s="1">
+        <v>14</v>
+      </c>
+      <c r="R24" s="1">
+        <v>15</v>
+      </c>
+      <c r="S24" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5">
+        <v>1</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5">
+        <v>2</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5">
+        <v>3</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5">
+        <v>4</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5">
+        <v>5</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5">
+        <v>6</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:S6"/>
+    <mergeCell ref="C7:S7"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:S9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A24:B24"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
     <col customWidth="true" max="1" min="1" width="18"/>
     <col customWidth="true" max="2" min="2" width="25"/>
     <col customWidth="true" max="3" min="3" width="10"/>
@@ -1519,56 +2874,56 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -1587,25 +2942,25 @@
         <v>8</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>8</v>
@@ -1628,25 +2983,25 @@
         <v>8</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>8</v>
@@ -1669,25 +3024,25 @@
         <v>8</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>8</v>
@@ -1710,25 +3065,25 @@
         <v>8</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>8</v>
@@ -1751,25 +3106,25 @@
         <v>8</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>8</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>8</v>
@@ -1792,25 +3147,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>8</v>
@@ -1825,6 +3180,88 @@
         <v>8</v>
       </c>
       <c r="M9" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M11" s="8" t="s">
         <v>8</v>
       </c>
     </row>
